--- a/NHIS variable list_Modified.xlsx
+++ b/NHIS variable list_Modified.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macpro/PycharmProjects/NHIS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B8A0785-AA58-374C-88D6-AD3721A09A4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A739DC75-96E8-FA4E-80D1-A67A264BE08C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17880" yWindow="760" windowWidth="11680" windowHeight="17600" xr2:uid="{AA949552-4F9F-40F0-90AF-3F34A678AD64}"/>
+    <workbookView xWindow="39460" yWindow="1240" windowWidth="22080" windowHeight="19540" xr2:uid="{AA949552-4F9F-40F0-90AF-3F34A678AD64}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="164">
   <si>
     <t>description</t>
   </si>
@@ -272,31 +272,7 @@
     <t>Opioid use - past 12 months</t>
   </si>
   <si>
-    <t>Opioid use - past 3 months</t>
-  </si>
-  <si>
-    <t>Opioid use for acute pain</t>
-  </si>
-  <si>
-    <t>Opioid use for chronic pain</t>
-  </si>
-  <si>
-    <t>Frequency of opioid use</t>
-  </si>
-  <si>
     <t>OPD12M_A</t>
-  </si>
-  <si>
-    <t>OPD3M_A</t>
-  </si>
-  <si>
-    <t>OPDACUTE_A</t>
-  </si>
-  <si>
-    <t>OPDCHRONIC_A</t>
-  </si>
-  <si>
-    <t>OPDFREQ_A</t>
   </si>
   <si>
     <t>secondary outcome</t>
@@ -588,7 +564,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -625,12 +601,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7030A0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -659,7 +629,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -677,15 +647,11 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -1002,7 +968,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C15A277-6A4B-4FED-94DF-816CADB374AA}">
-  <dimension ref="B1:G80"/>
+  <dimension ref="B1:G76"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -1013,7 +979,7 @@
   <sheetData>
     <row r="1" spans="2:5" s="1" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B1" s="2" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>0</v>
@@ -1022,7 +988,7 @@
         <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.2">
@@ -1035,7 +1001,7 @@
       <c r="D2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="14"/>
+      <c r="E2" s="12"/>
     </row>
     <row r="3" spans="2:5" ht="16" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
@@ -1047,7 +1013,7 @@
       <c r="D3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="15"/>
+      <c r="E3" s="13"/>
     </row>
     <row r="4" spans="2:5" ht="16" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
@@ -1059,7 +1025,7 @@
       <c r="D4" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="15"/>
+      <c r="E4" s="13"/>
     </row>
     <row r="5" spans="2:5" ht="16" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
@@ -1071,7 +1037,7 @@
       <c r="D5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="15"/>
+      <c r="E5" s="13"/>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
@@ -1083,38 +1049,38 @@
       <c r="D6" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="14"/>
+      <c r="E6" s="12"/>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="C7" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E7" s="14"/>
+      <c r="E7" s="12"/>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="C8" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E8" s="14"/>
+      <c r="E8" s="12"/>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>2</v>
@@ -1122,10 +1088,10 @@
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>2</v>
@@ -1133,22 +1099,22 @@
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="C11" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E11" s="14"/>
+      <c r="E11" s="12"/>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="C12" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>2</v>
@@ -1156,10 +1122,10 @@
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C13" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>29</v>
@@ -1167,10 +1133,10 @@
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="C14" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>29</v>
@@ -1222,10 +1188,10 @@
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C19" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>32</v>
@@ -1233,10 +1199,10 @@
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C20" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>32</v>
@@ -1244,10 +1210,10 @@
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C21" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>32</v>
@@ -1255,10 +1221,10 @@
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C22" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>32</v>
@@ -1266,10 +1232,10 @@
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C23" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>32</v>
@@ -1277,10 +1243,10 @@
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="C24" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>32</v>
@@ -1288,10 +1254,10 @@
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="C25" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>32</v>
@@ -1299,10 +1265,10 @@
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C26" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>32</v>
@@ -1310,10 +1276,10 @@
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="C27" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>32</v>
@@ -1607,10 +1573,10 @@
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B54" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C54" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>7</v>
@@ -1618,10 +1584,10 @@
     </row>
     <row r="55" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B55" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C55" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>7</v>
@@ -1629,10 +1595,10 @@
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B56" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="C56" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>7</v>
@@ -1640,10 +1606,10 @@
     </row>
     <row r="57" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B57" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="C57" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>7</v>
@@ -1651,10 +1617,10 @@
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B58" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="C58" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>7</v>
@@ -1662,10 +1628,10 @@
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B59" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="C59" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>7</v>
@@ -1673,10 +1639,10 @@
     </row>
     <row r="60" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B60" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="C60" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>7</v>
@@ -1684,10 +1650,10 @@
     </row>
     <row r="61" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B61" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="C61" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>7</v>
@@ -1695,10 +1661,10 @@
     </row>
     <row r="62" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B62" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="C62" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>7</v>
@@ -1706,10 +1672,10 @@
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B63" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="C63" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>7</v>
@@ -1717,10 +1683,10 @@
     </row>
     <row r="64" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B64" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="C64" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="D64" s="4" t="s">
         <v>7</v>
@@ -1728,10 +1694,10 @@
     </row>
     <row r="65" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B65" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="C65" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>7</v>
@@ -1739,182 +1705,138 @@
     </row>
     <row r="66" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B66" t="s">
+        <v>100</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="D66" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="C66" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="D66" s="6" t="s">
-        <v>116</v>
-      </c>
       <c r="G66" s="5" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="67" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B67" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
     </row>
     <row r="68" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B68" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
     </row>
     <row r="69" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B69" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
     </row>
     <row r="70" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B70" t="s">
-        <v>123</v>
-      </c>
-      <c r="C70" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="D70" s="10" t="s">
-        <v>87</v>
+        <v>115</v>
+      </c>
+      <c r="C70" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D70" s="9" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="71" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B71" t="s">
-        <v>124</v>
-      </c>
-      <c r="C71" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="D71" s="10" t="s">
-        <v>87</v>
+        <v>116</v>
+      </c>
+      <c r="C71" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="D71" s="9" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="72" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B72" t="s">
-        <v>125</v>
-      </c>
-      <c r="C72" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="D72" s="10" t="s">
-        <v>87</v>
+        <v>117</v>
+      </c>
+      <c r="C72" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D72" s="9" t="s">
+        <v>79</v>
       </c>
       <c r="G72" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
     </row>
     <row r="73" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B73" t="s">
-        <v>126</v>
-      </c>
-      <c r="C73" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="D73" s="10" t="s">
-        <v>87</v>
+        <v>118</v>
+      </c>
+      <c r="C73" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="D73" s="9" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="74" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B74" t="s">
-        <v>127</v>
-      </c>
-      <c r="C74" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="D74" s="10" t="s">
-        <v>87</v>
+        <v>119</v>
+      </c>
+      <c r="C74" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="D74" s="9" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="75" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B75" t="s">
-        <v>128</v>
-      </c>
-      <c r="C75" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="D75" s="10" t="s">
-        <v>87</v>
+        <v>120</v>
+      </c>
+      <c r="C75" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D75" s="9" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="76" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B76" t="s">
-        <v>82</v>
-      </c>
-      <c r="C76" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="C76" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="D76" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="77" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B77" t="s">
-        <v>83</v>
-      </c>
-      <c r="C77" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="D77" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="78" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B78" t="s">
-        <v>84</v>
-      </c>
-      <c r="C78" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="D78" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="G78" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="79" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B79" t="s">
-        <v>85</v>
-      </c>
-      <c r="C79" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="D79" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="80" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B80" t="s">
-        <v>86</v>
-      </c>
-      <c r="C80" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="D80" s="9" t="s">
-        <v>87</v>
+      <c r="D76" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G76" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>

--- a/NHIS variable list_Modified.xlsx
+++ b/NHIS variable list_Modified.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11210"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macpro/PycharmProjects/NHIS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ncaandt-my.sharepoint.com/personal/hmoradi_ncat_edu/Documents/05_Projects/NHIS-surface/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A739DC75-96E8-FA4E-80D1-A67A264BE08C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39460" yWindow="1240" windowWidth="22080" windowHeight="19540" xr2:uid="{AA949552-4F9F-40F0-90AF-3F34A678AD64}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{AA949552-4F9F-40F0-90AF-3F34A678AD64}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -969,15 +969,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C15A277-6A4B-4FED-94DF-816CADB374AA}">
   <dimension ref="B1:G76"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="23.1640625" customWidth="1"/>
-    <col min="3" max="3" width="37.5" customWidth="1"/>
-    <col min="4" max="4" width="17.83203125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="23.1328125" customWidth="1"/>
+    <col min="3" max="3" width="37.46484375" customWidth="1"/>
+    <col min="4" max="4" width="17.796875" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" s="1" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:5" s="1" customFormat="1" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B1" s="2" t="s">
         <v>133</v>
       </c>
@@ -991,7 +991,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>3</v>
       </c>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="E2" s="12"/>
     </row>
-    <row r="3" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:5" ht="15.4" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
         <v>5</v>
       </c>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="E3" s="13"/>
     </row>
-    <row r="4" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:5" ht="15.4" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
         <v>8</v>
       </c>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="E4" s="13"/>
     </row>
-    <row r="5" spans="2:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:5" ht="15.4" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
         <v>19</v>
       </c>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="E5" s="13"/>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
         <v>25</v>
       </c>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="E6" s="12"/>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
         <v>126</v>
       </c>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="E7" s="12"/>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
         <v>160</v>
       </c>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E8" s="12"/>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
         <v>161</v>
       </c>
@@ -1086,7 +1086,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
         <v>162</v>
       </c>
@@ -1097,7 +1097,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
         <v>130</v>
       </c>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="E11" s="12"/>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
         <v>132</v>
       </c>
@@ -1120,7 +1120,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
         <v>154</v>
       </c>
@@ -1131,7 +1131,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
         <v>155</v>
       </c>
@@ -1142,7 +1142,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
         <v>21</v>
       </c>
@@ -1153,7 +1153,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
         <v>30</v>
       </c>
@@ -1164,7 +1164,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
         <v>33</v>
       </c>
@@ -1175,7 +1175,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
         <v>35</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
         <v>80</v>
       </c>
@@ -1197,7 +1197,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B20" t="s">
         <v>81</v>
       </c>
@@ -1208,7 +1208,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
         <v>82</v>
       </c>
@@ -1219,7 +1219,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
         <v>86</v>
       </c>
@@ -1230,7 +1230,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
         <v>87</v>
       </c>
@@ -1241,7 +1241,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
         <v>88</v>
       </c>
@@ -1252,7 +1252,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
         <v>96</v>
       </c>
@@ -1263,7 +1263,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
         <v>98</v>
       </c>
@@ -1274,7 +1274,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B27" t="s">
         <v>128</v>
       </c>
@@ -1285,7 +1285,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B28" t="s">
         <v>11</v>
       </c>
@@ -1296,7 +1296,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B29" t="s">
         <v>13</v>
       </c>
@@ -1307,7 +1307,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
         <v>15</v>
       </c>
@@ -1318,7 +1318,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B31" t="s">
         <v>17</v>
       </c>
@@ -1329,7 +1329,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
         <v>23</v>
       </c>
@@ -1340,7 +1340,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B33" t="s">
         <v>27</v>
       </c>
@@ -1351,7 +1351,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B34" t="s">
         <v>37</v>
       </c>
@@ -1362,7 +1362,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B35" t="s">
         <v>39</v>
       </c>
@@ -1373,7 +1373,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B36" t="s">
         <v>40</v>
       </c>
@@ -1384,7 +1384,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B37" t="s">
         <v>41</v>
       </c>
@@ -1395,7 +1395,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B38" t="s">
         <v>42</v>
       </c>
@@ -1406,7 +1406,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B39" t="s">
         <v>43</v>
       </c>
@@ -1417,7 +1417,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B40" t="s">
         <v>44</v>
       </c>
@@ -1428,7 +1428,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B41" t="s">
         <v>45</v>
       </c>
@@ -1439,7 +1439,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B42" t="s">
         <v>53</v>
       </c>
@@ -1450,7 +1450,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B43" t="s">
         <v>55</v>
       </c>
@@ -1461,7 +1461,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B44" t="s">
         <v>57</v>
       </c>
@@ -1472,7 +1472,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B45" t="s">
         <v>59</v>
       </c>
@@ -1483,7 +1483,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B46" t="s">
         <v>60</v>
       </c>
@@ -1494,7 +1494,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B47" t="s">
         <v>61</v>
       </c>
@@ -1505,7 +1505,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B48" t="s">
         <v>67</v>
       </c>
@@ -1516,7 +1516,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B49" t="s">
         <v>68</v>
       </c>
@@ -1527,7 +1527,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B50" t="s">
         <v>70</v>
       </c>
@@ -1538,7 +1538,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B51" t="s">
         <v>74</v>
       </c>
@@ -1549,7 +1549,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="52" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B52" t="s">
         <v>75</v>
       </c>
@@ -1560,7 +1560,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="53" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B53" t="s">
         <v>76</v>
       </c>
@@ -1571,7 +1571,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B54" t="s">
         <v>94</v>
       </c>
@@ -1582,7 +1582,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B55" t="s">
         <v>95</v>
       </c>
@@ -1593,7 +1593,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="56" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B56" t="s">
         <v>136</v>
       </c>
@@ -1604,7 +1604,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="57" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B57" t="s">
         <v>137</v>
       </c>
@@ -1615,7 +1615,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="58" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B58" t="s">
         <v>139</v>
       </c>
@@ -1626,7 +1626,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="59" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B59" t="s">
         <v>140</v>
       </c>
@@ -1637,7 +1637,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="60" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B60" t="s">
         <v>144</v>
       </c>
@@ -1648,7 +1648,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="61" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B61" t="s">
         <v>145</v>
       </c>
@@ -1659,7 +1659,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="62" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B62" t="s">
         <v>147</v>
       </c>
@@ -1670,7 +1670,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="63" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B63" t="s">
         <v>151</v>
       </c>
@@ -1681,7 +1681,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="64" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B64" t="s">
         <v>152</v>
       </c>
@@ -1692,7 +1692,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="65" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B65" t="s">
         <v>153</v>
       </c>
@@ -1703,7 +1703,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="66" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B66" t="s">
         <v>100</v>
       </c>
@@ -1717,7 +1717,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="67" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B67" t="s">
         <v>101</v>
       </c>
@@ -1731,7 +1731,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="68" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B68" t="s">
         <v>102</v>
       </c>
@@ -1745,7 +1745,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="69" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B69" t="s">
         <v>103</v>
       </c>
@@ -1756,7 +1756,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="70" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B70" t="s">
         <v>115</v>
       </c>
@@ -1767,7 +1767,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="71" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B71" t="s">
         <v>116</v>
       </c>
@@ -1778,7 +1778,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="72" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B72" t="s">
         <v>117</v>
       </c>
@@ -1792,7 +1792,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="73" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B73" t="s">
         <v>118</v>
       </c>
@@ -1803,7 +1803,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="74" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B74" t="s">
         <v>119</v>
       </c>
@@ -1814,7 +1814,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="75" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B75" t="s">
         <v>120</v>
       </c>
@@ -1825,7 +1825,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="76" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B76" t="s">
         <v>78</v>
       </c>
